--- a/src/test/resources/TestCoverageDashboard_UAT.xlsx
+++ b/src/test/resources/TestCoverageDashboard_UAT.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
     </mc:Choice>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>Functional Area</t>
   </si>
@@ -158,6 +158,12 @@
   </si>
   <si>
     <t>03/30/2026 05:50:29 PM</t>
+  </si>
+  <si>
+    <t>04/14/2026 06:36:12 PM</t>
+  </si>
+  <si>
+    <t>04/14/2026 07:55:21 PM</t>
   </si>
 </sst>
 </file>
@@ -3455,14 +3461,14 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.7109375" customWidth="1"/>
-    <col min="2" max="3" width="24.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="34.7109375"/>
+    <col min="2" max="3" customWidth="true" width="24.5703125"/>
+    <col min="4" max="4" customWidth="true" width="14.7109375"/>
+    <col min="5" max="5" customWidth="true" width="9.140625"/>
+    <col min="6" max="6" customWidth="true" width="8.140625"/>
+    <col min="7" max="7" customWidth="true" width="7.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.28515625"/>
+    <col min="9" max="9" customWidth="true" width="24.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3470,7 +3476,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="26">
         <v>46111.738459328706</v>
@@ -3511,29 +3517,29 @@
       <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="9">
-        <v>31</v>
-      </c>
-      <c r="C3" s="9">
-        <v>29</v>
-      </c>
-      <c r="D3" s="9">
-        <v>2</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="B3" s="9" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="7" t="n">
         <f>IF(B3=0,"",C3/B3)</f>
-        <v>0.93548387096774188</v>
-      </c>
-      <c r="G3" s="7">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="G3" s="7" t="n">
         <f>IFERROR(D3/B3,0)</f>
-        <v>6.4516129032258063E-2</v>
-      </c>
-      <c r="H3" s="7">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="H3" s="7" t="n">
         <f>IFERROR(E3/B3,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
@@ -3552,162 +3558,162 @@
       <c r="E4" s="10">
         <v>0</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="7" t="n">
         <f t="shared" ref="F4:F16" si="0">IF(B4=0,"",C4/B4)</f>
-        <v>1</v>
-      </c>
-      <c r="G4" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <f t="shared" ref="G4:G14" si="1">IFERROR(D4/B4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="7" t="n">
         <f t="shared" ref="H4:H14" si="2">IFERROR(E4/B4,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="9">
-        <v>9</v>
-      </c>
-      <c r="C5" s="9">
-        <v>9</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="B5" s="9" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G5" s="7">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="H5" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="10">
-        <v>7</v>
-      </c>
-      <c r="C6" s="10">
-        <v>7</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="B6" s="10" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="9">
-        <v>17</v>
-      </c>
-      <c r="C7" s="9">
-        <v>17</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="B7" s="9" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="9">
-        <v>7</v>
-      </c>
-      <c r="C8" s="10">
-        <v>7</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="B8" s="9" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9">
-        <v>8</v>
-      </c>
-      <c r="C9" s="9">
-        <v>8</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="B9" s="9" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I9" s="2"/>
     </row>
@@ -3723,13 +3729,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I10" s="2"/>
     </row>
@@ -3745,13 +3751,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I11" s="2"/>
     </row>
@@ -3767,13 +3773,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I12" s="2"/>
     </row>
@@ -3781,29 +3787,29 @@
       <c r="A13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="9">
-        <v>1</v>
-      </c>
-      <c r="C13" s="9">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="B13" s="9" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="7">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="G13" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H13" s="7">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="H13" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I13" s="2"/>
     </row>
@@ -3819,13 +3825,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I14" s="2"/>
     </row>
@@ -3833,29 +3839,29 @@
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="9">
-        <v>10</v>
-      </c>
-      <c r="C15" s="9">
-        <v>10</v>
-      </c>
-      <c r="D15" s="9">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="B15" s="9" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G15" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <f>IFERROR(D15/B15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <f t="shared" ref="H15:H17" si="3">IFERROR(E15/B15,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
@@ -3870,46 +3876,46 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="7" t="n">
         <f>IFERROR(D16/B16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="7" t="n">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="14" t="n">
         <f>SUM(B3:B16)</f>
-        <v>98</v>
-      </c>
-      <c r="C17" s="14">
+        <v>104.0</v>
+      </c>
+      <c r="C17" s="14" t="n">
         <f>SUM(C3:C15)</f>
-        <v>95</v>
-      </c>
-      <c r="D17" s="14">
+        <v>99.0</v>
+      </c>
+      <c r="D17" s="14" t="n">
         <f>SUM(D3:D15)</f>
-        <v>3</v>
-      </c>
-      <c r="E17" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="E17" s="14" t="n">
         <f>SUM(E3:E15)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="15" t="n">
         <f t="shared" ref="F17" si="4">IFERROR(C17/B17,0)</f>
-        <v>0.96938775510204078</v>
-      </c>
-      <c r="G17" s="15">
+        <v>0.9519230769230769</v>
+      </c>
+      <c r="G17" s="15" t="n">
         <f t="shared" ref="G17" si="5">IFERROR(D17/B17,0)</f>
-        <v>3.0612244897959183E-2</v>
-      </c>
-      <c r="H17" s="15">
+        <v>0.04807692307692308</v>
+      </c>
+      <c r="H17" s="15" t="n">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -3954,12 +3960,12 @@
   <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="49.140625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.7109375"/>
+    <col min="2" max="2" customWidth="true" width="23.5703125"/>
+    <col min="5" max="5" customWidth="true" width="18.0"/>
+    <col min="6" max="6" customWidth="true" width="25.7109375"/>
+    <col min="7" max="7" customWidth="true" width="15.85546875"/>
+    <col min="8" max="8" customWidth="true" width="49.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="33" x14ac:dyDescent="0.25">
@@ -3988,7 +3994,7 @@
       </c>
       <c r="H3" s="5" t="str">
         <f>TestCoverage!B1</f>
-        <v>03/30/2026 05:50:29 PM</v>
+        <v>04/14/2026 07:55:21 PM</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -4003,9 +4009,9 @@
       <c r="G4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="17" t="n">
         <f>TestCoverage!B17</f>
-        <v>98</v>
+        <v>104.0</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -4020,9 +4026,9 @@
       <c r="G5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="17" t="n">
         <f>TestCoverage!C17</f>
-        <v>95</v>
+        <v>99.0</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -4037,9 +4043,9 @@
       <c r="G6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="17" t="n">
         <f>TestCoverage!D17</f>
-        <v>3</v>
+        <v>5.0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -4054,9 +4060,9 @@
       <c r="G7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="17" t="n">
         <f>TestCoverage!E17</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -4071,9 +4077,9 @@
       <c r="G8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="16" t="n">
         <f>IFERROR(H5/H4,"")</f>
-        <v>0.96938775510204078</v>
+        <v>0.9519230769230769</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -4123,14 +4129,14 @@
   <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" customWidth="1"/>
-    <col min="9" max="9" width="39.140625" customWidth="1"/>
-    <col min="10" max="10" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="37.85546875"/>
+    <col min="2" max="2" customWidth="true" width="14.0"/>
+    <col min="4" max="5" customWidth="true" width="13.85546875"/>
+    <col min="6" max="6" customWidth="true" width="10.42578125"/>
+    <col min="7" max="7" customWidth="true" width="26.140625"/>
+    <col min="8" max="8" customWidth="true" width="23.5703125"/>
+    <col min="9" max="9" customWidth="true" width="39.140625"/>
+    <col min="10" max="10" customWidth="true" width="33.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4158,7 +4164,7 @@
       <c r="H1" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>34</v>
       </c>
       <c r="J1" s="24" t="s">
@@ -4168,31 +4174,31 @@
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="str">
         <f>TestCoverage!A13 &amp; " (" &amp; IFERROR(TestCoverage!B13+0,0) &amp; ")"</f>
-        <v>Accessibility (Section 508 Compliance) (1)</v>
-      </c>
-      <c r="B2" s="20">
+        <v>Accessibility (Section 508 Compliance) (7)</v>
+      </c>
+      <c r="B2" s="20" t="n">
         <f>TestCoverage!F13</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="20">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="C2" s="20" t="n">
         <f>TestCoverage!G13</f>
-        <v>1</v>
-      </c>
-      <c r="D2" s="20">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D2" s="20" t="n">
         <f>TestCoverage!H13</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="20" t="n">
         <f>C2 + D2</f>
-        <v>1</v>
-      </c>
-      <c r="F2" s="19">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="F2" s="19" t="n">
         <f>TestCoverage!B13</f>
-        <v>1</v>
-      </c>
-      <c r="G2" s="18">
+        <v>7.0</v>
+      </c>
+      <c r="G2" s="18" t="n">
         <f>IF($F2=0,1,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H2" s="19" t="str">
         <f>IF(G2=100%,"Not Automated","")</f>
@@ -4200,7 +4206,7 @@
       </c>
       <c r="I2" s="19" t="str">
         <f>IF(AND(C2&gt;0,F2&gt;0),"⚠️ "&amp;A2,A2)</f>
-        <v>⚠️ Accessibility (Section 508 Compliance) (1)</v>
+        <v>⚠️ Accessibility (Section 508 Compliance) (7)</v>
       </c>
       <c r="J2" s="19" t="str">
         <f>IF(D2=100%,"Blocked","")</f>
@@ -4212,29 +4218,29 @@
         <f>TestCoverage!A3 &amp; " (" &amp; IFERROR(TestCoverage!B3+0,0) &amp; ")"</f>
         <v>Validations &amp; Business Rules (31)</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="20" t="n">
         <f>TestCoverage!F3</f>
-        <v>0.93548387096774188</v>
-      </c>
-      <c r="C3" s="20">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <f>TestCoverage!G3</f>
-        <v>6.4516129032258063E-2</v>
-      </c>
-      <c r="D3" s="20">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="D3" s="20" t="n">
         <f>TestCoverage!H3</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="20" t="n">
         <f>C3 + D3</f>
-        <v>6.4516129032258063E-2</v>
-      </c>
-      <c r="F3" s="19">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="F3" s="19" t="n">
         <f>TestCoverage!B3</f>
-        <v>31</v>
-      </c>
-      <c r="G3" s="18">
+        <v>31.0</v>
+      </c>
+      <c r="G3" s="18" t="n">
         <f>IF($F3=0,1,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H3" s="19" t="str">
         <f>IF(G3=100%,"Not Automated","")</f>
@@ -4254,29 +4260,29 @@
         <f>TestCoverage!A4 &amp; " (" &amp; IFERROR(TestCoverage!B4+0,0) &amp; ")"</f>
         <v>RAI Management (8)</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="20" t="n">
         <f>TestCoverage!F4</f>
-        <v>1</v>
-      </c>
-      <c r="C4" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="C4" s="20" t="n">
         <f>TestCoverage!G4</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D4" s="20" t="n">
         <f>TestCoverage!H4</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="20" t="n">
         <f>C4 + D4</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="19" t="n">
         <f>TestCoverage!B4</f>
-        <v>8</v>
-      </c>
-      <c r="G4" s="18">
+        <v>8.0</v>
+      </c>
+      <c r="G4" s="18" t="n">
         <f>IF($F4=0,1,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H4" s="19" t="str">
         <f>IF(G4=100%,"Not Automated","")</f>
@@ -4296,29 +4302,29 @@
         <f>TestCoverage!A5 &amp; " (" &amp; IFERROR(TestCoverage!B5+0,0) &amp; ")"</f>
         <v>SRT Review (9)</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="20" t="n">
         <f>TestCoverage!F5</f>
-        <v>1</v>
-      </c>
-      <c r="C5" s="20">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="C5" s="20" t="n">
         <f>TestCoverage!G5</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="20">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="D5" s="20" t="n">
         <f>TestCoverage!H5</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="20" t="n">
         <f>C5 + D5</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="19">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F5" s="19" t="n">
         <f>TestCoverage!B5</f>
-        <v>9</v>
-      </c>
-      <c r="G5" s="18">
+        <v>9.0</v>
+      </c>
+      <c r="G5" s="18" t="n">
         <f>IF($F5=0,1,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H5" s="19" t="str">
         <f>IF(G5=100%,"Not Automated","")</f>
@@ -4326,7 +4332,7 @@
       </c>
       <c r="I5" s="19" t="str">
         <f>IF(AND(C5&gt;0,F5&gt;0),"⚠️ "&amp;A5,A5)</f>
-        <v>SRT Review (9)</v>
+        <v>⚠️ SRT Review (9)</v>
       </c>
       <c r="J5" s="19" t="str">
         <f>IF(D5=100%,"Blocked","")</f>
@@ -4338,29 +4344,29 @@
         <f>TestCoverage!A6 &amp; " (" &amp; IFERROR(TestCoverage!B6+0,0) &amp; ")"</f>
         <v>Workflow &amp; Status Transitions (7)</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="20" t="n">
         <f>TestCoverage!F6</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="C6" s="20" t="n">
         <f>TestCoverage!G6</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="20" t="n">
         <f>TestCoverage!H6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="20" t="n">
         <f>C6 + D6</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="19" t="n">
         <f>TestCoverage!B6</f>
-        <v>7</v>
-      </c>
-      <c r="G6" s="18">
+        <v>7.0</v>
+      </c>
+      <c r="G6" s="18" t="n">
         <f>IF($F6=0,1,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H6" s="19" t="str">
         <f>IF(G6=100%,"Not Automated","")</f>
@@ -4380,29 +4386,29 @@
         <f>TestCoverage!A7 &amp; " (" &amp; IFERROR(TestCoverage!B7+0,0) &amp; ")"</f>
         <v>Record Lifecycle Management (17)</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="20" t="n">
         <f>TestCoverage!F7</f>
-        <v>1</v>
-      </c>
-      <c r="C7" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="C7" s="20" t="n">
         <f>TestCoverage!G7</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="20" t="n">
         <f>TestCoverage!H7</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="20" t="n">
         <f>C7 + D7</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="19" t="n">
         <f>TestCoverage!B7</f>
-        <v>17</v>
-      </c>
-      <c r="G7" s="18">
+        <v>17.0</v>
+      </c>
+      <c r="G7" s="18" t="n">
         <f>IF($F7=0,1,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H7" s="19" t="str">
         <f>IF(G7=100%,"Not Automated","")</f>
@@ -4422,29 +4428,29 @@
         <f>TestCoverage!A8 &amp; " (" &amp; IFERROR(TestCoverage!B8+0,0) &amp; ")"</f>
         <v>User Access &amp; Permissions (7)</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="20" t="n">
         <f>TestCoverage!F8</f>
-        <v>1</v>
-      </c>
-      <c r="C8" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="C8" s="20" t="n">
         <f>TestCoverage!G8</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="20" t="n">
         <f>TestCoverage!H8</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="20" t="n">
         <f>C8 + D8</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="19" t="n">
         <f>TestCoverage!B8</f>
-        <v>7</v>
-      </c>
-      <c r="G8" s="18">
+        <v>7.0</v>
+      </c>
+      <c r="G8" s="18" t="n">
         <f>IF($F8=0,1,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H8" s="19" t="str">
         <f>IF(G8=100%,"Not Automated","")</f>
@@ -4464,29 +4470,29 @@
         <f>TestCoverage!A9 &amp; " (" &amp; IFERROR(TestCoverage!B9+0,0) &amp; ")"</f>
         <v>Assignment &amp; Routing (8)</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="20" t="n">
         <f>TestCoverage!F9</f>
-        <v>1</v>
-      </c>
-      <c r="C9" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="C9" s="20" t="n">
         <f>TestCoverage!G9</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="20" t="n">
         <f>TestCoverage!H9</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="20" t="n">
         <f>C9 + D9</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="19" t="n">
         <f>TestCoverage!B9</f>
-        <v>8</v>
-      </c>
-      <c r="G9" s="18">
+        <v>8.0</v>
+      </c>
+      <c r="G9" s="18" t="n">
         <f>IF($F9=0,1,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H9" s="19" t="str">
         <f>IF(G9=100%,"Not Automated","")</f>
@@ -4510,25 +4516,25 @@
         <f>TestCoverage!F10</f>
         <v/>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="20" t="n">
         <f>TestCoverage!G10</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="20" t="n">
         <f>TestCoverage!H10</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="20" t="n">
         <f>C10 + D10</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="19" t="n">
         <f>TestCoverage!B10</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="18" t="n">
         <f>IF($F10=0,1,0)</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="H10" s="19" t="str">
         <f>IF(G10=100%,"Not Automated","")</f>
@@ -4552,25 +4558,25 @@
         <f>TestCoverage!F11</f>
         <v/>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="20" t="n">
         <f>TestCoverage!G11</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="20" t="n">
         <f>TestCoverage!H11</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="20" t="n">
         <f>C11 + D11</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="19" t="n">
         <f>TestCoverage!B11</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="18" t="n">
         <f>IF($F11=0,1,0)</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="H11" s="19" t="str">
         <f>IF(G11=100%,"Not Automated","")</f>
@@ -4594,25 +4600,25 @@
         <f>TestCoverage!F12</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="20" t="n">
         <f>TestCoverage!G12</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="20" t="n">
         <f>TestCoverage!H12</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="20" t="n">
         <f>C12 + D12</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="19" t="n">
         <f>TestCoverage!B12</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="18" t="n">
         <f>IF($F12=0,1,0)</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="H12" s="19" t="str">
         <f>IF(G12=100%,"Not Automated","")</f>
@@ -4636,25 +4642,25 @@
         <f>TestCoverage!F14</f>
         <v/>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="20" t="n">
         <f>TestCoverage!G14</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="20" t="n">
         <f>TestCoverage!H14</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="20" t="n">
         <f>C13 + D13</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="19" t="n">
         <f>TestCoverage!B14</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <f>IF($F13=0,1,0)</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="H13" s="19" t="str">
         <f>IF(G13=100%,"Not Automated","")</f>
@@ -4674,29 +4680,29 @@
         <f>TestCoverage!A15 &amp; " (" &amp; IFERROR(TestCoverage!B15+0,0) &amp; ")"</f>
         <v>Timeline &amp; SLA Management (10)</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="20" t="n">
         <f>TestCoverage!F15</f>
-        <v>1</v>
-      </c>
-      <c r="C14" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="C14" s="20" t="n">
         <f>TestCoverage!G15</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D14" s="20" t="n">
         <f>TestCoverage!H15</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="20" t="n">
         <f>C14 + D14</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="19" t="n">
         <f>TestCoverage!B15</f>
-        <v>10</v>
-      </c>
-      <c r="G14" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="G14" s="18" t="n">
         <f>IF($F14=0,1,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H14" s="19" t="str">
         <f>IF(G14=100%,"Not Automated","")</f>
@@ -4720,25 +4726,25 @@
         <f>TestCoverage!F16</f>
         <v/>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="20" t="n">
         <f>TestCoverage!G16</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="D15" s="20" t="n">
         <f>TestCoverage!H16</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="20" t="n">
         <f>C15 + D15</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="19">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="19" t="n">
         <f>TestCoverage!B16</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="18" t="n">
         <f>IF($F15=0,1,0)</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="H15" s="19" t="str">
         <f>IF(G15=100%,"Not Automated","")</f>
@@ -4756,28 +4762,28 @@
     <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="str">
         <f>TestCoverage!A17 &amp; " (" &amp; TestCoverage!B17 &amp; ")"</f>
-        <v>TOTAL (98)</v>
-      </c>
-      <c r="B16" s="20">
+        <v>TOTAL (104)</v>
+      </c>
+      <c r="B16" s="20" t="n">
         <f>TestCoverage!F17</f>
-        <v>0.96938775510204078</v>
-      </c>
-      <c r="C16" s="20">
+        <v>0.9519230769230769</v>
+      </c>
+      <c r="C16" s="20" t="n">
         <f>TestCoverage!G17</f>
-        <v>3.0612244897959183E-2</v>
-      </c>
-      <c r="D16" s="20">
+        <v>0.04807692307692308</v>
+      </c>
+      <c r="D16" s="20" t="n">
         <f>TestCoverage!H17</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="E16" s="20"/>
-      <c r="F16" s="19">
+      <c r="F16" s="19" t="n">
         <f>TestCoverage!B17</f>
-        <v>98</v>
-      </c>
-      <c r="G16" s="18">
+        <v>104.0</v>
+      </c>
+      <c r="G16" s="18" t="n">
         <f>COUNTIF(F2:F14,0)/COUNTA(A2:A14)</f>
-        <v>0.30769230769230771</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>

--- a/src/test/resources/TestCoverageDashboard_UAT.xlsx
+++ b/src/test/resources/TestCoverageDashboard_UAT.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85F9470-2A13-493E-8672-FC876370B32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8028B45D-2255-4807-8531-D2A14AC4F13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCoverage" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Functional Area</t>
   </si>
@@ -155,12 +155,6 @@
   </si>
   <si>
     <t>SRT Review</t>
-  </si>
-  <si>
-    <t>03/30/2026 05:50:29 PM</t>
-  </si>
-  <si>
-    <t>04/14/2026 06:36:12 PM</t>
   </si>
   <si>
     <t>04/14/2026 07:55:21 PM</t>
@@ -730,16 +724,16 @@
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>⚠️ Accessibility (Section 508 Compliance) (1)</c:v>
+                  <c:v>⚠️ Accessibility (Section 508 Compliance) (7)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>RAI Management (8)</c:v>
+                  <c:v>RAI Management (0)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>SRT Review (9)</c:v>
+                  <c:v>⚠️ SRT Review (9)</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Workflow &amp; Status Transitions (7)</c:v>
@@ -781,16 +775,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.7142857142857143</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.93548387096774188</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0.88888888888888884</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -917,16 +911,16 @@
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>⚠️ Accessibility (Section 508 Compliance) (1)</c:v>
+                  <c:v>⚠️ Accessibility (Section 508 Compliance) (7)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>RAI Management (8)</c:v>
+                  <c:v>RAI Management (0)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>SRT Review (9)</c:v>
+                  <c:v>⚠️ SRT Review (9)</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Workflow &amp; Status Transitions (7)</c:v>
@@ -968,7 +962,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0.2857142857142857</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>6.4516129032258063E-2</c:v>
@@ -977,7 +971,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.1111111111111111</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1094,7 +1088,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1128,7 +1121,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1162,7 +1154,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1196,7 +1187,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1230,7 +1220,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1264,7 +1253,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1298,7 +1286,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1332,7 +1319,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1366,7 +1352,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1400,7 +1385,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1434,7 +1418,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1468,7 +1451,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1502,7 +1484,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1572,16 +1553,16 @@
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>⚠️ Accessibility (Section 508 Compliance) (1)</c:v>
+                  <c:v>⚠️ Accessibility (Section 508 Compliance) (7)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>RAI Management (8)</c:v>
+                  <c:v>RAI Management (0)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>SRT Review (9)</c:v>
+                  <c:v>⚠️ SRT Review (9)</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Workflow &amp; Status Transitions (7)</c:v>
@@ -1759,7 +1740,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1793,7 +1773,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1827,7 +1806,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1861,7 +1839,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1895,7 +1872,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1929,7 +1905,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1963,7 +1938,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -1978,7 +1952,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DB60A831-B2E9-49A9-A145-8DFDC78443C6}" type="CELLRANGE">
+                    <a:fld id="{790F3C88-3556-4E84-ABD6-47E74284D28D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2012,7 +1986,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A21B692F-5060-4905-9EDE-A5C9939029F8}" type="CELLRANGE">
+                    <a:fld id="{54D2C8E6-4290-4BED-B173-24809A83B89E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2046,7 +2020,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{38271A87-C9BC-4937-9DCF-AD30AD97B06E}" type="CELLRANGE">
+                    <a:fld id="{15205FA6-89BC-4BC1-961A-D771F890966E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2080,7 +2054,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F3C3B93A-6402-415F-B72B-8310DFC3EC1E}" type="CELLRANGE">
+                    <a:fld id="{B45DCD9F-2D67-4ABD-8358-1121801DFC42}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2133,7 +2107,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2148,7 +2121,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7090F557-D22A-4F3B-B8DD-D81313A742D7}" type="CELLRANGE">
+                    <a:fld id="{50886B49-E2FC-4567-8A3D-67A8B473095F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2236,16 +2209,16 @@
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>⚠️ Accessibility (Section 508 Compliance) (1)</c:v>
+                  <c:v>⚠️ Accessibility (Section 508 Compliance) (7)</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>RAI Management (8)</c:v>
+                  <c:v>RAI Management (0)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>SRT Review (9)</c:v>
+                  <c:v>⚠️ SRT Review (9)</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Workflow &amp; Status Transitions (7)</c:v>
@@ -2293,7 +2266,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2337,6 +2310,9 @@
                 <c15:f>Dashboard_Data!$H$2:$H$15</c15:f>
                 <c15:dlblRangeCache>
                   <c:ptCount val="14"/>
+                  <c:pt idx="2">
+                    <c:v>Not Automated</c:v>
+                  </c:pt>
                   <c:pt idx="8">
                     <c:v>Not Automated</c:v>
                   </c:pt>
@@ -3461,14 +3437,14 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="34.7109375"/>
-    <col min="2" max="3" customWidth="true" width="24.5703125"/>
-    <col min="4" max="4" customWidth="true" width="14.7109375"/>
-    <col min="5" max="5" customWidth="true" width="9.140625"/>
-    <col min="6" max="6" customWidth="true" width="8.140625"/>
-    <col min="7" max="7" customWidth="true" width="7.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.28515625"/>
-    <col min="9" max="9" customWidth="true" width="24.0"/>
+    <col min="1" max="1" width="34.7109375" customWidth="1"/>
+    <col min="2" max="3" width="24.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3476,7 +3452,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C1" s="26">
         <v>46111.738459328706</v>
@@ -3517,203 +3493,195 @@
       <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="9" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="B3" s="9">
+        <v>31</v>
+      </c>
+      <c r="C3" s="9">
+        <v>29</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
         <f>IF(B3=0,"",C3/B3)</f>
-        <v>0.9354838709677419</v>
-      </c>
-      <c r="G3" s="7" t="n">
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="G3" s="7">
         <f>IFERROR(D3/B3,0)</f>
-        <v>0.06451612903225806</v>
-      </c>
-      <c r="H3" s="7" t="n">
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="H3" s="7">
         <f>IFERROR(E3/B3,0)</f>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="10">
-        <v>8</v>
-      </c>
-      <c r="C4" s="10">
-        <v>8</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0</v>
-      </c>
-      <c r="E4" s="10">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="7" t="str">
         <f t="shared" ref="F4:F16" si="0">IF(B4=0,"",C4/B4)</f>
-        <v>1.0</v>
-      </c>
-      <c r="G4" s="7" t="n">
+        <v/>
+      </c>
+      <c r="G4" s="7">
         <f t="shared" ref="G4:G14" si="1">IFERROR(D4/B4,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
         <f t="shared" ref="H4:H14" si="2">IFERROR(E4/B4,0)</f>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="7" t="n">
+      <c r="B5" s="9">
+        <v>9</v>
+      </c>
+      <c r="C5" s="9">
+        <v>8</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
         <f t="shared" si="0"/>
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="G5" s="7" t="n">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="G5" s="7">
         <f t="shared" si="1"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="10" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="7" t="n">
+      <c r="B6" s="10">
+        <v>7</v>
+      </c>
+      <c r="C6" s="10">
+        <v>7</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="7" t="n">
+      <c r="B7" s="9">
+        <v>17</v>
+      </c>
+      <c r="C7" s="9">
+        <v>17</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="B8" s="9">
+        <v>7</v>
+      </c>
+      <c r="C8" s="10">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="9" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="7" t="n">
+      <c r="B9" s="9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9">
+        <v>8</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2"/>
     </row>
@@ -3729,13 +3697,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2"/>
     </row>
@@ -3751,13 +3719,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2"/>
     </row>
@@ -3773,13 +3741,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2"/>
     </row>
@@ -3787,29 +3755,29 @@
       <c r="A13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F13" s="7" t="n">
+      <c r="B13" s="9">
+        <v>7</v>
+      </c>
+      <c r="C13" s="9">
+        <v>5</v>
+      </c>
+      <c r="D13" s="9">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7">
         <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="7">
         <f t="shared" si="1"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2"/>
     </row>
@@ -3825,13 +3793,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2"/>
     </row>
@@ -3839,29 +3807,29 @@
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="9" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="7" t="n">
+      <c r="B15" s="9">
+        <v>10</v>
+      </c>
+      <c r="C15" s="9">
+        <v>10</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7">
         <f>IFERROR(D15/B15,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
         <f t="shared" ref="H15:H17" si="3">IFERROR(E15/B15,0)</f>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
@@ -3876,46 +3844,46 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="7">
         <f>IFERROR(D16/B16,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
         <f t="shared" si="3"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="14">
         <f>SUM(B3:B16)</f>
-        <v>104.0</v>
-      </c>
-      <c r="C17" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="C17" s="14">
         <f>SUM(C3:C15)</f>
-        <v>99.0</v>
-      </c>
-      <c r="D17" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="D17" s="14">
         <f>SUM(D3:D15)</f>
-        <v>5.0</v>
-      </c>
-      <c r="E17" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="14">
         <f>SUM(E3:E15)</f>
-        <v>0.0</v>
-      </c>
-      <c r="F17" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
         <f t="shared" ref="F17" si="4">IFERROR(C17/B17,0)</f>
-        <v>0.9519230769230769</v>
-      </c>
-      <c r="G17" s="15" t="n">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="G17" s="15">
         <f t="shared" ref="G17" si="5">IFERROR(D17/B17,0)</f>
-        <v>0.04807692307692308</v>
-      </c>
-      <c r="H17" s="15" t="n">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="H17" s="15">
         <f t="shared" si="3"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3960,12 +3928,12 @@
   <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="14.7109375"/>
-    <col min="2" max="2" customWidth="true" width="23.5703125"/>
-    <col min="5" max="5" customWidth="true" width="18.0"/>
-    <col min="6" max="6" customWidth="true" width="25.7109375"/>
-    <col min="7" max="7" customWidth="true" width="15.85546875"/>
-    <col min="8" max="8" customWidth="true" width="49.140625"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="49.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="33" x14ac:dyDescent="0.25">
@@ -4009,9 +3977,9 @@
       <c r="G4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="17">
         <f>TestCoverage!B17</f>
-        <v>104.0</v>
+        <v>96</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -4026,9 +3994,9 @@
       <c r="G5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="17">
         <f>TestCoverage!C17</f>
-        <v>99.0</v>
+        <v>91</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -4043,9 +4011,9 @@
       <c r="G6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="17">
         <f>TestCoverage!D17</f>
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -4060,9 +4028,9 @@
       <c r="G7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="17">
         <f>TestCoverage!E17</f>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -4077,9 +4045,9 @@
       <c r="G8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="16">
         <f>IFERROR(H5/H4,"")</f>
-        <v>0.9519230769230769</v>
+        <v>0.94791666666666663</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -4129,14 +4097,14 @@
   <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="37.85546875"/>
-    <col min="2" max="2" customWidth="true" width="14.0"/>
-    <col min="4" max="5" customWidth="true" width="13.85546875"/>
-    <col min="6" max="6" customWidth="true" width="10.42578125"/>
-    <col min="7" max="7" customWidth="true" width="26.140625"/>
-    <col min="8" max="8" customWidth="true" width="23.5703125"/>
-    <col min="9" max="9" customWidth="true" width="39.140625"/>
-    <col min="10" max="10" customWidth="true" width="33.7109375"/>
+    <col min="1" max="1" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="4" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="26.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" customWidth="1"/>
+    <col min="9" max="9" width="39.140625" customWidth="1"/>
+    <col min="10" max="10" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4164,7 +4132,7 @@
       <c r="H1" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>34</v>
       </c>
       <c r="J1" s="24" t="s">
@@ -4176,40 +4144,40 @@
         <f>TestCoverage!A13 &amp; " (" &amp; IFERROR(TestCoverage!B13+0,0) &amp; ")"</f>
         <v>Accessibility (Section 508 Compliance) (7)</v>
       </c>
-      <c r="B2" s="20" t="n">
+      <c r="B2" s="20">
         <f>TestCoverage!F13</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="20">
         <f>TestCoverage!G13</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="20">
         <f>TestCoverage!H13</f>
-        <v>0.0</v>
-      </c>
-      <c r="E2" s="20" t="n">
-        <f>C2 + D2</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="20">
+        <f t="shared" ref="E2:E15" si="0">C2 + D2</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="F2" s="19" t="n">
+      <c r="F2" s="19">
         <f>TestCoverage!B13</f>
-        <v>7.0</v>
-      </c>
-      <c r="G2" s="18" t="n">
-        <f>IF($F2=0,1,0)</f>
-        <v>0.0</v>
+        <v>7</v>
+      </c>
+      <c r="G2" s="18">
+        <f t="shared" ref="G2:G15" si="1">IF($F2=0,1,0)</f>
+        <v>0</v>
       </c>
       <c r="H2" s="19" t="str">
-        <f>IF(G2=100%,"Not Automated","")</f>
+        <f t="shared" ref="H2:H15" si="2">IF(G2=100%,"Not Automated","")</f>
         <v/>
       </c>
       <c r="I2" s="19" t="str">
-        <f>IF(AND(C2&gt;0,F2&gt;0),"⚠️ "&amp;A2,A2)</f>
+        <f t="shared" ref="I2:I15" si="3">IF(AND(C2&gt;0,F2&gt;0),"⚠️ "&amp;A2,A2)</f>
         <v>⚠️ Accessibility (Section 508 Compliance) (7)</v>
       </c>
       <c r="J2" s="19" t="str">
-        <f>IF(D2=100%,"Blocked","")</f>
+        <f t="shared" ref="J2:J15" si="4">IF(D2=100%,"Blocked","")</f>
         <v/>
       </c>
     </row>
@@ -4218,82 +4186,82 @@
         <f>TestCoverage!A3 &amp; " (" &amp; IFERROR(TestCoverage!B3+0,0) &amp; ")"</f>
         <v>Validations &amp; Business Rules (31)</v>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" s="20">
         <f>TestCoverage!F3</f>
-        <v>0.9354838709677419</v>
-      </c>
-      <c r="C3" s="20" t="n">
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="C3" s="20">
         <f>TestCoverage!G3</f>
-        <v>0.06451612903225806</v>
-      </c>
-      <c r="D3" s="20" t="n">
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="D3" s="20">
         <f>TestCoverage!H3</f>
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="20" t="n">
-        <f>C3 + D3</f>
-        <v>0.06451612903225806</v>
-      </c>
-      <c r="F3" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="20">
+        <f t="shared" si="0"/>
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="F3" s="19">
         <f>TestCoverage!B3</f>
-        <v>31.0</v>
-      </c>
-      <c r="G3" s="18" t="n">
-        <f>IF($F3=0,1,0)</f>
-        <v>0.0</v>
+        <v>31</v>
+      </c>
+      <c r="G3" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H3" s="19" t="str">
-        <f>IF(G3=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I3" s="19" t="str">
-        <f>IF(AND(C3&gt;0,F3&gt;0),"⚠️ "&amp;A3,A3)</f>
+        <f t="shared" si="3"/>
         <v>⚠️ Validations &amp; Business Rules (31)</v>
       </c>
       <c r="J3" s="19" t="str">
-        <f>IF(D3=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="str">
         <f>TestCoverage!A4 &amp; " (" &amp; IFERROR(TestCoverage!B4+0,0) &amp; ")"</f>
-        <v>RAI Management (8)</v>
-      </c>
-      <c r="B4" s="20" t="n">
+        <v>RAI Management (0)</v>
+      </c>
+      <c r="B4" s="20" t="str">
         <f>TestCoverage!F4</f>
-        <v>1.0</v>
-      </c>
-      <c r="C4" s="20" t="n">
+        <v/>
+      </c>
+      <c r="C4" s="20">
         <f>TestCoverage!G4</f>
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="20">
         <f>TestCoverage!H4</f>
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="20" t="n">
-        <f>C4 + D4</f>
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="19">
         <f>TestCoverage!B4</f>
-        <v>8.0</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <f>IF($F4=0,1,0)</f>
-        <v>0.0</v>
+        <v>0</v>
+      </c>
+      <c r="G4" s="18">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H4" s="19" t="str">
-        <f>IF(G4=100%,"Not Automated","")</f>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Not Automated</v>
       </c>
       <c r="I4" s="19" t="str">
-        <f>IF(AND(C4&gt;0,F4&gt;0),"⚠️ "&amp;A4,A4)</f>
-        <v>RAI Management (8)</v>
+        <f t="shared" si="3"/>
+        <v>RAI Management (0)</v>
       </c>
       <c r="J4" s="19" t="str">
-        <f>IF(D4=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4302,40 +4270,40 @@
         <f>TestCoverage!A5 &amp; " (" &amp; IFERROR(TestCoverage!B5+0,0) &amp; ")"</f>
         <v>SRT Review (9)</v>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="20">
         <f>TestCoverage!F5</f>
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="C5" s="20" t="n">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="C5" s="20">
         <f>TestCoverage!G5</f>
         <v>0.1111111111111111</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="20">
         <f>TestCoverage!H5</f>
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="20" t="n">
-        <f>C5 + D5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="20">
+        <f t="shared" si="0"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="19">
         <f>TestCoverage!B5</f>
-        <v>9.0</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <f>IF($F5=0,1,0)</f>
-        <v>0.0</v>
+        <v>9</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H5" s="19" t="str">
-        <f>IF(G5=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I5" s="19" t="str">
-        <f>IF(AND(C5&gt;0,F5&gt;0),"⚠️ "&amp;A5,A5)</f>
+        <f t="shared" si="3"/>
         <v>⚠️ SRT Review (9)</v>
       </c>
       <c r="J5" s="19" t="str">
-        <f>IF(D5=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4344,40 +4312,40 @@
         <f>TestCoverage!A6 &amp; " (" &amp; IFERROR(TestCoverage!B6+0,0) &amp; ")"</f>
         <v>Workflow &amp; Status Transitions (7)</v>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="20">
         <f>TestCoverage!F6</f>
-        <v>1.0</v>
-      </c>
-      <c r="C6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="20">
         <f>TestCoverage!G6</f>
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="20">
         <f>TestCoverage!H6</f>
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <f>C6 + D6</f>
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="19">
         <f>TestCoverage!B6</f>
-        <v>7.0</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <f>IF($F6=0,1,0)</f>
-        <v>0.0</v>
+        <v>7</v>
+      </c>
+      <c r="G6" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H6" s="19" t="str">
-        <f>IF(G6=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I6" s="19" t="str">
-        <f>IF(AND(C6&gt;0,F6&gt;0),"⚠️ "&amp;A6,A6)</f>
+        <f t="shared" si="3"/>
         <v>Workflow &amp; Status Transitions (7)</v>
       </c>
       <c r="J6" s="19" t="str">
-        <f>IF(D6=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4386,40 +4354,40 @@
         <f>TestCoverage!A7 &amp; " (" &amp; IFERROR(TestCoverage!B7+0,0) &amp; ")"</f>
         <v>Record Lifecycle Management (17)</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="20">
         <f>TestCoverage!F7</f>
-        <v>1.0</v>
-      </c>
-      <c r="C7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="20">
         <f>TestCoverage!G7</f>
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="20">
         <f>TestCoverage!H7</f>
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="20" t="n">
-        <f>C7 + D7</f>
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="19">
         <f>TestCoverage!B7</f>
-        <v>17.0</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <f>IF($F7=0,1,0)</f>
-        <v>0.0</v>
+        <v>17</v>
+      </c>
+      <c r="G7" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H7" s="19" t="str">
-        <f>IF(G7=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I7" s="19" t="str">
-        <f>IF(AND(C7&gt;0,F7&gt;0),"⚠️ "&amp;A7,A7)</f>
+        <f t="shared" si="3"/>
         <v>Record Lifecycle Management (17)</v>
       </c>
       <c r="J7" s="19" t="str">
-        <f>IF(D7=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4428,40 +4396,40 @@
         <f>TestCoverage!A8 &amp; " (" &amp; IFERROR(TestCoverage!B8+0,0) &amp; ")"</f>
         <v>User Access &amp; Permissions (7)</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="20">
         <f>TestCoverage!F8</f>
-        <v>1.0</v>
-      </c>
-      <c r="C8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="20">
         <f>TestCoverage!G8</f>
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="20">
         <f>TestCoverage!H8</f>
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <f>C8 + D8</f>
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="19">
         <f>TestCoverage!B8</f>
-        <v>7.0</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <f>IF($F8=0,1,0)</f>
-        <v>0.0</v>
+        <v>7</v>
+      </c>
+      <c r="G8" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H8" s="19" t="str">
-        <f>IF(G8=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I8" s="19" t="str">
-        <f>IF(AND(C8&gt;0,F8&gt;0),"⚠️ "&amp;A8,A8)</f>
+        <f t="shared" si="3"/>
         <v>User Access &amp; Permissions (7)</v>
       </c>
       <c r="J8" s="19" t="str">
-        <f>IF(D8=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4470,40 +4438,40 @@
         <f>TestCoverage!A9 &amp; " (" &amp; IFERROR(TestCoverage!B9+0,0) &amp; ")"</f>
         <v>Assignment &amp; Routing (8)</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="20">
         <f>TestCoverage!F9</f>
-        <v>1.0</v>
-      </c>
-      <c r="C9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="20">
         <f>TestCoverage!G9</f>
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="20">
         <f>TestCoverage!H9</f>
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="20" t="n">
-        <f>C9 + D9</f>
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="19">
         <f>TestCoverage!B9</f>
-        <v>8.0</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <f>IF($F9=0,1,0)</f>
-        <v>0.0</v>
+        <v>8</v>
+      </c>
+      <c r="G9" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H9" s="19" t="str">
-        <f>IF(G9=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I9" s="19" t="str">
-        <f>IF(AND(C9&gt;0,F9&gt;0),"⚠️ "&amp;A9,A9)</f>
+        <f t="shared" si="3"/>
         <v>Assignment &amp; Routing (8)</v>
       </c>
       <c r="J9" s="19" t="str">
-        <f>IF(D9=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4516,36 +4484,36 @@
         <f>TestCoverage!F10</f>
         <v/>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="20">
         <f>TestCoverage!G10</f>
-        <v>0.0</v>
-      </c>
-      <c r="D10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="20">
         <f>TestCoverage!H10</f>
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <f>C10 + D10</f>
-        <v>0.0</v>
-      </c>
-      <c r="F10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="19">
         <f>TestCoverage!B10</f>
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <f>IF($F10=0,1,0)</f>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G10" s="18">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H10" s="19" t="str">
-        <f>IF(G10=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I10" s="19" t="str">
-        <f>IF(AND(C10&gt;0,F10&gt;0),"⚠️ "&amp;A10,A10)</f>
+        <f t="shared" si="3"/>
         <v>API End To End (0)</v>
       </c>
       <c r="J10" s="19" t="str">
-        <f>IF(D10=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4558,36 +4526,36 @@
         <f>TestCoverage!F11</f>
         <v/>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="20">
         <f>TestCoverage!G11</f>
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="20">
         <f>TestCoverage!H11</f>
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <f>C11 + D11</f>
-        <v>0.0</v>
-      </c>
-      <c r="F11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="19">
         <f>TestCoverage!B11</f>
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <f>IF($F11=0,1,0)</f>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H11" s="19" t="str">
-        <f>IF(G11=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I11" s="19" t="str">
-        <f>IF(AND(C11&gt;0,F11&gt;0),"⚠️ "&amp;A11,A11)</f>
+        <f t="shared" si="3"/>
         <v>Search &amp; Filters (0)</v>
       </c>
       <c r="J11" s="19" t="str">
-        <f>IF(D11=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4600,36 +4568,36 @@
         <f>TestCoverage!F12</f>
         <v/>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="20">
         <f>TestCoverage!G12</f>
-        <v>0.0</v>
-      </c>
-      <c r="D12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="20">
         <f>TestCoverage!H12</f>
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <f>C12 + D12</f>
-        <v>0.0</v>
-      </c>
-      <c r="F12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="19">
         <f>TestCoverage!B12</f>
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <f>IF($F12=0,1,0)</f>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H12" s="19" t="str">
-        <f>IF(G12=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I12" s="19" t="str">
-        <f>IF(AND(C12&gt;0,F12&gt;0),"⚠️ "&amp;A12,A12)</f>
+        <f t="shared" si="3"/>
         <v>Reporting &amp; Data Export (0)</v>
       </c>
       <c r="J12" s="19" t="str">
-        <f>IF(D12=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4642,36 +4610,36 @@
         <f>TestCoverage!F14</f>
         <v/>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="20">
         <f>TestCoverage!G14</f>
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="20">
         <f>TestCoverage!H14</f>
-        <v>0.0</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <f>C13 + D13</f>
-        <v>0.0</v>
-      </c>
-      <c r="F13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="19">
         <f>TestCoverage!B14</f>
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <f>IF($F13=0,1,0)</f>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H13" s="19" t="str">
-        <f>IF(G13=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I13" s="19" t="str">
-        <f>IF(AND(C13&gt;0,F13&gt;0),"⚠️ "&amp;A13,A13)</f>
+        <f t="shared" si="3"/>
         <v>Email Notifications &amp; Alerts (0)</v>
       </c>
       <c r="J13" s="19" t="str">
-        <f>IF(D13=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4680,40 +4648,40 @@
         <f>TestCoverage!A15 &amp; " (" &amp; IFERROR(TestCoverage!B15+0,0) &amp; ")"</f>
         <v>Timeline &amp; SLA Management (10)</v>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="20">
         <f>TestCoverage!F15</f>
-        <v>1.0</v>
-      </c>
-      <c r="C14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="20">
         <f>TestCoverage!G15</f>
-        <v>0.0</v>
-      </c>
-      <c r="D14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="20">
         <f>TestCoverage!H15</f>
-        <v>0.0</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <f>C14 + D14</f>
-        <v>0.0</v>
-      </c>
-      <c r="F14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="19">
         <f>TestCoverage!B15</f>
-        <v>10.0</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <f>IF($F14=0,1,0)</f>
-        <v>0.0</v>
+        <v>10</v>
+      </c>
+      <c r="G14" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="H14" s="19" t="str">
-        <f>IF(G14=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I14" s="19" t="str">
-        <f>IF(AND(C14&gt;0,F14&gt;0),"⚠️ "&amp;A14,A14)</f>
+        <f t="shared" si="3"/>
         <v>Timeline &amp; SLA Management (10)</v>
       </c>
       <c r="J14" s="19" t="str">
-        <f>IF(D14=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4726,64 +4694,64 @@
         <f>TestCoverage!F16</f>
         <v/>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="20">
         <f>TestCoverage!G16</f>
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="20">
         <f>TestCoverage!H16</f>
-        <v>0.0</v>
-      </c>
-      <c r="E15" s="20" t="n">
-        <f>C15 + D15</f>
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="19">
         <f>TestCoverage!B16</f>
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <f>IF($F15=0,1,0)</f>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H15" s="19" t="str">
-        <f>IF(G15=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I15" s="19" t="str">
-        <f>IF(AND(C15&gt;0,F15&gt;0),"⚠️ "&amp;A15,A15)</f>
+        <f t="shared" si="3"/>
         <v>Document Management (0)</v>
       </c>
       <c r="J15" s="19" t="str">
-        <f>IF(D15=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="str">
         <f>TestCoverage!A17 &amp; " (" &amp; TestCoverage!B17 &amp; ")"</f>
-        <v>TOTAL (104)</v>
-      </c>
-      <c r="B16" s="20" t="n">
+        <v>TOTAL (96)</v>
+      </c>
+      <c r="B16" s="20">
         <f>TestCoverage!F17</f>
-        <v>0.9519230769230769</v>
-      </c>
-      <c r="C16" s="20" t="n">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="C16" s="20">
         <f>TestCoverage!G17</f>
-        <v>0.04807692307692308</v>
-      </c>
-      <c r="D16" s="20" t="n">
+        <v>5.2083333333333336E-2</v>
+      </c>
+      <c r="D16" s="20">
         <f>TestCoverage!H17</f>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E16" s="20"/>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="19">
         <f>TestCoverage!B17</f>
-        <v>104.0</v>
-      </c>
-      <c r="G16" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="G16" s="18">
         <f>COUNTIF(F2:F14,0)/COUNTA(A2:A14)</f>
-        <v>0.3076923076923077</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
